--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>110701701</v>
       </c>
       <c r="B9" t="n">
-        <v>56543</v>
+        <v>57522</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,21 +1501,23 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vackermyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583893.7922092003</v>
+        <v>583893</v>
       </c>
       <c r="R9" t="n">
-        <v>7086395.770834208</v>
+        <v>7086396</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>110701701</v>
       </c>
       <c r="B9" t="n">
-        <v>57522</v>
+        <v>57525</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>110701701</v>
       </c>
       <c r="B9" t="n">
-        <v>57525</v>
+        <v>57527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>110701701</v>
       </c>
       <c r="B9" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -1484,11 +1484,6 @@
       <c r="E9" t="n">
         <v>103021</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>110701701</v>
       </c>
       <c r="B9" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,6 +1483,11 @@
       </c>
       <c r="E9" t="n">
         <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>110701701</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110701213</v>
+        <v>110698005</v>
       </c>
       <c r="B2" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vackermyran, Ång</t>
+          <t>Stor-Kärmsjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583980.0430533572</v>
+        <v>583850</v>
       </c>
       <c r="R2" t="n">
-        <v>7086387.947589207</v>
+        <v>7086494</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +771,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110701569</v>
+        <v>110702005</v>
       </c>
       <c r="B3" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +794,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vackermyran, Ång</t>
+          <t>Stor-Kärmsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583922.4112773607</v>
+        <v>583891</v>
       </c>
       <c r="R3" t="n">
-        <v>7086332.200575014</v>
+        <v>7086382</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +852,9 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +869,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110701692</v>
+        <v>110700651</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583889.8475300337</v>
+        <v>583946</v>
       </c>
       <c r="R4" t="n">
-        <v>7086394.783831461</v>
+        <v>7086468</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,51 +989,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110701693</v>
+        <v>110700299</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Kärmsjön, Ång</t>
+          <t>Vackermyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583886.1107279561</v>
+        <v>583971</v>
       </c>
       <c r="R5" t="n">
-        <v>7086369.565959821</v>
+        <v>7086514</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,27 +1085,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110700651</v>
+        <v>110697910</v>
       </c>
       <c r="B6" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,35 +1108,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vackermyran, Ång</t>
+          <t>Stor-Kärmsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583945.7073575848</v>
+        <v>583815</v>
       </c>
       <c r="R6" t="n">
-        <v>7086467.226455003</v>
+        <v>7086457</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110702269</v>
+        <v>110701569</v>
       </c>
       <c r="B7" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583806.7383986146</v>
+        <v>583923</v>
       </c>
       <c r="R7" t="n">
-        <v>7086466.588500027</v>
+        <v>7086332</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110697910</v>
+        <v>110701207</v>
       </c>
       <c r="B8" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,35 +1324,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Kärmsjön, Ång</t>
+          <t>Vackermyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583814.9458514397</v>
+        <v>583980</v>
       </c>
       <c r="R8" t="n">
-        <v>7086456.673210785</v>
+        <v>7086388</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,7 +1384,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1394,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,27 +1409,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110701701</v>
+        <v>110702056</v>
       </c>
       <c r="B9" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,42 +1432,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vackermyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583893</v>
+        <v>583833</v>
       </c>
       <c r="R9" t="n">
-        <v>7086396</v>
+        <v>7086414</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1547,19 +1490,9 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,15 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110701164</v>
+        <v>110701213</v>
       </c>
       <c r="B10" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1627,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583980.0430533572</v>
+        <v>583980</v>
       </c>
       <c r="R10" t="n">
-        <v>7086387.947589207</v>
+        <v>7086388</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1699,15 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110702056</v>
+        <v>110701701</v>
       </c>
       <c r="B11" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,35 +1638,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vackermyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583833.7375945009</v>
+        <v>583893</v>
       </c>
       <c r="R11" t="n">
-        <v>7086413.992114238</v>
+        <v>7086396</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1775,7 +1705,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1715,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,15 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110702005</v>
+        <v>110697992</v>
       </c>
       <c r="B12" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,35 +1753,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-Kärmsjön, Ång</t>
+          <t>Vackermyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583891.0832808333</v>
+        <v>583854</v>
       </c>
       <c r="R12" t="n">
-        <v>7086381.597086154</v>
+        <v>7086492</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1888,7 +1813,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1823,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,49 +1838,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110701207</v>
+        <v>110701164</v>
       </c>
       <c r="B13" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583980.0430533572</v>
+        <v>583980</v>
       </c>
       <c r="R13" t="n">
-        <v>7086387.947589207</v>
+        <v>7086388</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2035,6 +1955,516 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110701692</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vackermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>583890</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7086394</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110701693</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Kärmsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583887</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7086370</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110700001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vackermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>583947</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7086520</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110702262</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vackermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583854</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7086492</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110702269</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vackermyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>583807</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7086467</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21345-2023 artfynd.xlsx
+++ b/artfynd/A 21345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110698005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110702005</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110700651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110700299</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110697910</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110701569</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110701207</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110702056</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110701213</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110701701</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110697992</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110701164</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110701692</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2161,6 +2231,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110701693</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2269,6 +2344,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110700001</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2367,6 +2447,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110702262</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,8 +2550,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110702269</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>